--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-isolat-microbiologique.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-isolat-microbiologique.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,16 +455,6 @@
   </si>
   <si>
     <t>Code isolat</t>
-  </si>
-  <si>
-    <t>fr-lm-isolat-microbiologique.choice[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-sujet-non-humain
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-sujet-non-humain</t>
-  </si>
-  <si>
-    <t>Sujet non humain ou Patient avec sujet non humain</t>
   </si>
   <si>
     <t>fr-lm-isolat-microbiologique.isolatMicrobiologique</t>
@@ -837,7 +827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.95703125" customWidth="true" bestFit="true"/>
@@ -2900,7 +2890,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2915,13 +2905,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2975,7 +2965,7 @@
         <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2989,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3072,7 +3062,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3089,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3115,13 +3105,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3172,7 +3162,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3189,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3215,13 +3205,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3272,7 +3262,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3289,10 +3279,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3315,13 +3305,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3372,7 +3362,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3389,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3400,10 +3390,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3415,13 +3405,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3472,13 +3462,13 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
@@ -3884,106 +3874,6 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
         <v>73</v>
       </c>
     </row>
